--- a/Ternimal sets.xlsx
+++ b/Ternimal sets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PCTemp\GPHH for Matrix Shop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PCTemp\IPPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93835C87-56F3-4F05-9A81-9E980E2F770C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A74FAA-91E4-4BC6-9B0E-2B12FD2626DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22605" yWindow="1725" windowWidth="23025" windowHeight="18630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
   <si>
     <t>Terminal</t>
   </si>
@@ -55,12 +55,6 @@
   </si>
   <si>
     <t>NOR</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>Weight of a job</t>
   </si>
   <si>
     <t>rJ</t>
@@ -117,6 +111,22 @@
   </si>
   <si>
     <r>
+      <t>station</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中所有作业完成所需时间</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>job</t>
     </r>
     <r>
@@ -127,8 +137,20 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>中下道序的消耗时间</t>
-    </r>
+      <t>释放时间</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Work remaining of the job</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WR</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统时间</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -143,7 +165,131 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>中本道序的消耗时间</t>
+      <t>交货期</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Index</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NCC</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Number of capabilities of a cell</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WRJ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Whether the current state of the RMC can undertake the job (1 if yes; 0 if no)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Configuration time</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RT</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>动</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>静态参数</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>静态</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>动态</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The number of operations that require this capability among the remaining operations</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOCR</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>station中能力的数量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>当前的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>station</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>的能力能否执行该</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>operation</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -159,16 +305,152 @@
         <family val="1"/>
         <charset val="134"/>
       </rPr>
-      <t>当前剩余工序数量</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>job权重</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
+      <t>中剩余</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>operation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的总消耗时间</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>job</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当前剩余</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>operation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数量</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>job</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中下道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>operation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的消耗时间</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>job</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中本道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>operation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的消耗时间</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>该</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
       <t>station</t>
     </r>
     <r>
@@ -176,75 +458,144 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中所有作业完成所需时间</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>job</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中剩余序的总消耗时间</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>job</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>释放时间</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Work remaining of the job</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WR</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>job</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>交货期</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>随机数</t>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的配置时间</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>station</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的序列中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>，符合该</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>station</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当前能力的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>operation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数量</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Task</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中可执行工序串的总时间</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Task</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>中可执行工序串的所需能力数量</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Task</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>中可执行工序串的工序数量</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The total time that an operation string can be executed in a job</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The number of required capabilites that an operation string can be executed in a job</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The number of operations that an operation string can be executed in a job</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TTOS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NCOS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOOS</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -252,7 +603,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,6 +643,45 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -367,7 +757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -382,6 +772,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -664,178 +1060,372 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.75" customWidth="1"/>
-    <col min="2" max="2" width="36.875" customWidth="1"/>
-    <col min="4" max="4" width="27.25" customWidth="1"/>
+    <col min="2" max="2" width="8.75" customWidth="1"/>
+    <col min="3" max="3" width="27.75" customWidth="1"/>
+    <col min="5" max="5" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="F5" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>16</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>17</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>18</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>19</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>20</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>21</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>22</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="3">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="3">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>36</v>
+      <c r="B18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
